--- a/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/프로젝트_일괄등록_양식.xlsx
+++ b/KNK업무시스템구축/01_HAIST_WORKS/app/static/templates/프로젝트_일괄등록_양식.xlsx
@@ -581,7 +581,7 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>1차 고객사 · 프로젝트명 · 모델명 · 수량 · 1차 납품 단가 · 1차 납품 금액 · 상태</t>
+          <t>고객사1 · 프로젝트명 · 모델명 · 수량 · 1차 납품 단가 · 1차 납품 금액 · 상태</t>
         </is>
       </c>
     </row>
@@ -607,7 +607,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>법인 경유 시만: 2차 고객사(최종) + 2차 납품 단가/금액(VND). 안 쓰면 비움</t>
+          <t>법인 경유 시만: 고객사2(최종) + 2차 납품 단가/금액(VND). 안 쓰면 비움</t>
         </is>
       </c>
     </row>
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="C13" s="3">
-        <f> 1차 고객사 납품 금액(합계 포함). 2차(최종) 금액은 참고용(합계 제외)</f>
+        <f> 고객사1 납품 금액(합계 포함). 2차(최종) 금액은 참고용(합계 제외)</f>
         <v/>
       </c>
     </row>
@@ -721,12 +721,12 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사 *</t>
+          <t>고객사1 *</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 (2단계 발주 시)</t>
         </is>
       </c>
@@ -747,13 +747,13 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 단가 *</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 금액 *</t>
         </is>
       </c>
@@ -804,7 +804,7 @@
       </c>
       <c r="R3" s="13" t="inlineStr">
         <is>
-          <t>영업담당</t>
+          <t>영업담당자</t>
         </is>
       </c>
       <c r="S3" s="13" t="inlineStr">
@@ -814,13 +814,13 @@
       </c>
       <c r="T3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 단가 (VND)</t>
         </is>
       </c>
       <c r="U3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 금액 (VND)</t>
         </is>
       </c>
@@ -977,12 +977,12 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사 *</t>
+          <t>고객사1 *</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 (2단계 발주 시)</t>
         </is>
       </c>
@@ -1003,13 +1003,13 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 단가 *</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 금액 *</t>
         </is>
       </c>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="R3" s="13" t="inlineStr">
         <is>
-          <t>영업담당</t>
+          <t>영업담당자</t>
         </is>
       </c>
       <c r="S3" s="13" t="inlineStr">
@@ -1070,13 +1070,13 @@
       </c>
       <c r="T3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 단가 (VND)</t>
         </is>
       </c>
       <c r="U3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 금액 (VND)</t>
         </is>
       </c>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사 *</t>
+          <t>고객사1 *</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 (2단계 발주 시)</t>
         </is>
       </c>
@@ -1259,13 +1259,13 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 단가 *</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 금액 *</t>
         </is>
       </c>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="R3" s="13" t="inlineStr">
         <is>
-          <t>영업담당</t>
+          <t>영업담당자</t>
         </is>
       </c>
       <c r="S3" s="13" t="inlineStr">
@@ -1326,13 +1326,13 @@
       </c>
       <c r="T3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 단가 (VND)</t>
         </is>
       </c>
       <c r="U3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 금액 (VND)</t>
         </is>
       </c>
@@ -1489,12 +1489,12 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사 *</t>
+          <t>고객사1 *</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 (2단계 발주 시)</t>
         </is>
       </c>
@@ -1515,13 +1515,13 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 단가 *</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 금액 *</t>
         </is>
       </c>
@@ -1572,7 +1572,7 @@
       </c>
       <c r="R3" s="13" t="inlineStr">
         <is>
-          <t>영업담당</t>
+          <t>영업담당자</t>
         </is>
       </c>
       <c r="S3" s="13" t="inlineStr">
@@ -1582,13 +1582,13 @@
       </c>
       <c r="T3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 단가 (VND)</t>
         </is>
       </c>
       <c r="U3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 금액 (VND)</t>
         </is>
       </c>
@@ -1745,12 +1745,12 @@
       </c>
       <c r="B3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사 *</t>
+          <t>고객사1 *</t>
         </is>
       </c>
       <c r="C3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 (2단계 발주 시)</t>
         </is>
       </c>
@@ -1771,13 +1771,13 @@
       </c>
       <c r="G3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 단가 *</t>
         </is>
       </c>
       <c r="H3" s="11" t="inlineStr">
         <is>
-          <t>1차 고객사
+          <t>고객사1
 납품 금액 *</t>
         </is>
       </c>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="R3" s="13" t="inlineStr">
         <is>
-          <t>영업담당</t>
+          <t>영업담당자</t>
         </is>
       </c>
       <c r="S3" s="13" t="inlineStr">
@@ -1838,13 +1838,13 @@
       </c>
       <c r="T3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 단가 (VND)</t>
         </is>
       </c>
       <c r="U3" s="12" t="inlineStr">
         <is>
-          <t>2차 고객사
+          <t>고객사2
 납품 금액 (VND)</t>
         </is>
       </c>
